--- a/CHECKLIST-ALFA-1/dist/Dados/registos_checklist.xlsx
+++ b/CHECKLIST-ALFA-1/dist/Dados/registos_checklist.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -504,9 +504,10 @@
     <col width="8" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="8" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="30" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="30" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -602,15 +603,20 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>Colunas</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>USB</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Portas de Vídeo</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
@@ -699,17 +705,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S2" s="4" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="4" t="inlineStr">
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="4" t="inlineStr">
         <is>
           <t>testes</t>
         </is>
@@ -798,17 +805,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S3" s="7" t="inlineStr"/>
       <c r="T3" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U3" s="7" t="inlineStr">
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V3" s="7" t="inlineStr">
         <is>
           <t>Danos para teste</t>
         </is>
@@ -897,17 +905,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S4" s="4" t="inlineStr"/>
       <c r="T4" s="3" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U4" s="4" t="inlineStr">
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
         <is>
           <t>teste</t>
         </is>
@@ -1000,19 +1009,349 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S5" s="7" t="inlineStr"/>
       <c r="T5" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U5" s="7" t="inlineStr">
+      <c r="U5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V5" s="7" t="inlineStr">
         <is>
           <t>teste</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>19/02/2026 21:53</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Guilherme</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>teste</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>ASUS System Product Name</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>221011108801049</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>AMD Ryzen 7 5800X3D 8-Core Processor</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>16 GB</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>DIMM</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>WD Blue SN570 1TB (932 GB) + Verbatim Vi550 S3 (477 GB)</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA GeForce RTX 3070</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>Sem observações</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>24/02/2026 19:43</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Guilherme</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>teste1</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>ASUS System Product Name</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>221011108801049</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>AMD Ryzen 7 5800X3D 8-Core Processor</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>16 GB</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>DIMM</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>WD Blue SN570 1TB (932 GB) + Verbatim Vi550 S3 (477 GB)</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>NVIDIA GeForce RTX 3070</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V7" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>24/02/2026 20:01</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Guilherme</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>teste2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>ASUS System Product Name</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>221011108801049</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>AMD Ryzen 7 5800X3D 8-Core Processor</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>16 GB</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>DIMM</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>xxx</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>WD Blue SN570 1TB (932 GB) + Verbatim Vi550 S3 (477 GB)</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA GeForce RTX 3070</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">teste alteração 2
+</t>
         </is>
       </c>
     </row>
